--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
         </is>
       </c>
     </row>
@@ -4878,13 +4878,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7057,8 +7057,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8824,8 +8824,8 @@
       <c r="T81" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U81" s="9" t="n">
-        <v>0</v>
+      <c r="U81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V81" s="9" t="n">
         <v>0</v>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9873,8 +9873,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -13263,7 +13263,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13395,7 +13395,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1537,7 +1541,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -831,20 +831,20 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>28680243</v>
+        <v>2101</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Yates Toastmasters</t>
+          <t>Florence Toastmasters</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -907,13 +907,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
+      <c r="X2" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -924,8 +924,14 @@
       <c r="AA2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -939,11 +945,11 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2101</v>
+        <v>3235</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Florence Toastmasters</t>
+          <t>North Alabama Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -961,28 +967,28 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
-        <v>46446</v>
+      <c r="M3" s="8" t="n">
+        <v>46387</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1006,13 +1012,13 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X3" s="10" t="n">
-        <v>5</v>
+      <c r="X3" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1020,17 +1026,13 @@
       <c r="Z3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" s="10" t="n">
-        <v>1</v>
+      <c r="AA3" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1044,15 +1046,15 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3235</v>
+        <v>4838</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>North Alabama Advanced Toastmasters</t>
+          <t>Research Park Toastmasters</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1066,70 +1068,70 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="Y4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O4" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="AC4" s="4" t="inlineStr"/>
     </row>
@@ -1145,15 +1147,15 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4838</v>
+        <v>9626</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Research Park Toastmasters</t>
+          <t>Speaking Easy Club</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1167,20 +1169,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1188,7 +1190,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1196,41 +1198,41 @@
       <c r="P5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC5" s="4" t="inlineStr"/>
     </row>
@@ -1246,15 +1248,15 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9626</v>
+        <v>651363</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Speaking Easy Club</t>
+          <t>VA Voices Toastmasters Club</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1268,20 +1270,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1289,51 +1291,55 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1343,19 +1349,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>651363</v>
+        <v>1325394</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>VA Voices Toastmasters Club</t>
+          <t>Circle of Champions Toastmasters</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1369,20 +1375,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1390,31 +1396,31 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U7" s="10" t="n">
-        <v>1</v>
+      <c r="U7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1438,9 @@
         <v>1</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1452,15 +1454,15 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1325394</v>
+        <v>1932</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Circle of Champions Toastmasters</t>
+          <t>Redstone Toastmasters Club</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1474,20 +1476,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1495,51 +1497,55 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="9" t="n">
-        <v>0</v>
+      <c r="S8" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
+      <c r="U8" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1553,15 +1559,15 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1932</v>
+        <v>1380024</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Redstone Toastmasters Club</t>
+          <t>SAIC Huntsville Toastmasters</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1575,20 +1581,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1596,55 +1602,51 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="10" t="n">
-        <v>2</v>
+      <c r="S9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="10" t="n">
-        <v>7</v>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="10" t="n">
-        <v>1</v>
+      <c r="Z9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1658,11 +1660,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1380024</v>
+        <v>960</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SAIC Huntsville Toastmasters</t>
+          <t>Tennessee Valley Toastmasters Club</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -1688,12 +1690,12 @@
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1701,13 +1703,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1730,8 +1732,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>0</v>
+      <c r="X10" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1743,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC10" s="4" t="inlineStr"/>
     </row>
@@ -1755,19 +1757,19 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>960</v>
+        <v>3963</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Tennessee Valley Toastmasters Club</t>
+          <t>Hi-Noon Toastmasters Club</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1781,20 +1783,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1802,22 +1804,22 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -1825,28 +1827,32 @@
       <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="9" t="n">
-        <v>0</v>
+      <c r="V11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1860,50 +1866,50 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3963</v>
+        <v>5606202</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Hi-Noon Toastmasters Club</t>
+          <t>Premier Providers</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
-        <v>46446</v>
+      <c r="M12" s="8" t="n">
+        <v>46387</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1917,17 +1923,17 @@
       <c r="R12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="10" t="n">
-        <v>4</v>
+      <c r="S12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1941,15 +1947,15 @@
       <c r="Z12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" s="10" t="n">
-        <v>1</v>
+      <c r="AA12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -1965,74 +1971,74 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5606202</v>
+        <v>3126</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Premier Providers</t>
+          <t>Protective Pacesetters Club</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" s="4" t="n">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="10" t="n">
-        <v>2</v>
+      <c r="S13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U13" s="10" t="n">
-        <v>1</v>
+      <c r="U13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2046,15 +2052,15 @@
       <c r="Z13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA13" s="9" t="n">
-        <v>0</v>
+      <c r="AA13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -2070,15 +2076,15 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3126</v>
+        <v>6054</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Protective Pacesetters Club</t>
+          <t>Strategic Speakers Club</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2092,20 +2098,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2113,13 +2119,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2130,20 +2136,20 @@
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="10" t="n">
-        <v>1</v>
+      <c r="T14" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2175,15 +2181,15 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6054</v>
+        <v>2600138</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Strategic Speakers Club</t>
+          <t>Von Braun Speakers</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2197,34 +2203,34 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>46446</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>46387</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2242,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="10" t="n">
-        <v>6</v>
+      <c r="X15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2256,17 +2262,13 @@
       <c r="Z15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA15" s="10" t="n">
-        <v>1</v>
+      <c r="AA15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2276,19 +2278,19 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2600138</v>
+        <v>4301984</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Von Braun Speakers</t>
+          <t>Choctaw Easy Speakers</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2302,28 +2304,28 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
-        <v>46387</v>
+      <c r="M16" s="8" t="n">
+        <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2347,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
+      <c r="X16" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" s="4" t="inlineStr"/>
     </row>
@@ -2381,15 +2383,15 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4301984</v>
+        <v>3176998</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Choctaw Easy Speakers</t>
+          <t>Greater Gadsden Speakers</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2403,20 +2405,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2424,7 +2426,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2454,19 +2456,19 @@
         <v>0</v>
       </c>
       <c r="X17" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
     </row>
@@ -2482,15 +2484,15 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3176998</v>
+        <v>9309</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Greater Gadsden Speakers</t>
+          <t>Power Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2504,20 +2506,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2525,7 +2527,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2548,26 +2550,26 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>0</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC18" s="4" t="inlineStr"/>
     </row>
@@ -2583,15 +2585,15 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9309</v>
+        <v>2199554</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Power Speakers Toastmasters Club</t>
+          <t>Summit Speakers</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2605,20 +2607,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2626,7 +2628,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2649,11 +2651,11 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="10" t="n">
-        <v>4</v>
+      <c r="V19" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>5</v>
@@ -2675,24 +2677,24 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2199554</v>
+        <v>1359</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Summit Speakers</t>
+          <t>A-OK Club</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2706,20 +2708,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2727,13 +2729,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2762,15 +2764,13 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="10" t="n">
-        <v>1</v>
+      <c r="Z20" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2785,15 +2785,15 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1359</v>
+        <v>6046</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>A-OK Club</t>
+          <t>All Rounders Club</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2810,17 +2810,17 @@
         <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2828,22 +2828,22 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="9" t="n">
         <v>0</v>
@@ -2852,19 +2852,19 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2884,15 +2884,15 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6046</v>
+        <v>3323744</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>All Rounders Club</t>
+          <t>Blue Nile Toastmasters, Memphis</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2906,20 +2906,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2927,7 +2927,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -2944,14 +2944,14 @@
       <c r="S22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2962,8 +2962,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -2983,15 +2983,15 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3323744</v>
+        <v>1449617</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Blue Nile Toastmasters, Memphis</t>
+          <t>Express Delivery Toastmasters</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3005,20 +3005,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3026,7 +3026,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3041,22 +3041,22 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -3082,15 +3082,15 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1449617</v>
+        <v>28677744</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Express Delivery Toastmasters</t>
+          <t>River City Toastmasters I</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
@@ -3117,15 +3117,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
-        <v>46446</v>
+      <c r="M24" s="8" t="n">
+        <v>46387</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="inlineStr">
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3160,11 +3160,11 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="10" t="n">
-        <v>1</v>
+      <c r="Z24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="4" t="inlineStr"/>
@@ -3181,15 +3181,15 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>28677744</v>
+        <v>28680243</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>River City Toastmasters I</t>
+          <t>Yates Toastmasters</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0</v>
@@ -3216,15 +3216,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
-        <v>46387</v>
+      <c r="M25" s="8" t="n">
+        <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="inlineStr">
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3253,17 +3253,17 @@
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="10" t="n">
-        <v>5</v>
+      <c r="X25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="4" t="inlineStr"/>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3302,20 +3302,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3323,7 +3323,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3347,7 +3347,7 @@
         <v>2</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3358,8 +3358,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3414,7 +3414,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3422,7 +3422,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3513,7 +3513,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3521,7 +3521,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3620,7 +3620,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3655,8 +3655,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3706,12 +3706,12 @@
       <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3719,7 +3719,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3805,12 +3805,12 @@
       <c r="K31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3818,7 +3818,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3904,12 +3904,12 @@
       <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3917,7 +3917,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4003,12 +4003,12 @@
       <c r="K33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4016,7 +4016,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4107,7 +4107,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4115,7 +4115,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4150,8 +4150,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="9" t="n">
         <v>0</v>
@@ -4206,7 +4206,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4300,12 +4300,12 @@
       <c r="K36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4313,7 +4313,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4348,8 +4348,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="9" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4412,7 +4412,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4503,7 +4503,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4597,12 +4597,12 @@
       <c r="K39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4610,7 +4610,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4696,12 +4696,12 @@
       <c r="K40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4709,16 +4709,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="9" t="n">
         <v>0</v>
@@ -4726,8 +4726,8 @@
       <c r="S40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="9" t="n">
-        <v>0</v>
+      <c r="T40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="9" t="n">
         <v>0</v>
@@ -4744,8 +4744,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4795,12 +4795,12 @@
       <c r="K41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="8" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4808,7 +4808,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4899,7 +4899,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4907,7 +4907,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4942,8 +4942,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="9" t="n">
         <v>0</v>
@@ -4993,12 +4993,12 @@
       <c r="K43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5006,7 +5006,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5094,12 +5094,12 @@
       <c r="K44" s="4" t="n">
         <v>-12</v>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5107,7 +5107,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5200,7 +5200,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5208,7 +5208,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5299,7 +5299,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5307,7 +5307,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5399,12 +5399,12 @@
       <c r="K47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5412,7 +5412,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5500,12 +5500,12 @@
       <c r="K48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5513,7 +5513,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5606,7 +5606,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5614,7 +5614,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5706,12 +5706,12 @@
       <c r="K50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L50" s="8" t="inlineStr">
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5719,7 +5719,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5807,12 +5807,12 @@
       <c r="K51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="8" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5820,7 +5820,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5913,7 +5913,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5921,7 +5921,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6013,12 +6013,12 @@
       <c r="K53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6114,12 +6114,12 @@
       <c r="K54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6127,7 +6127,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6220,7 +6220,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6228,7 +6228,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6320,12 +6320,12 @@
       <c r="K56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L56" s="8" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6333,7 +6333,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6421,12 +6421,12 @@
       <c r="K57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="8" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6434,7 +6434,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6522,12 +6522,12 @@
       <c r="K58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="8" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6535,7 +6535,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6621,12 +6621,12 @@
       <c r="K59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L59" s="8" t="inlineStr">
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6634,7 +6634,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6720,12 +6720,12 @@
       <c r="K60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L60" s="8" t="inlineStr">
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6733,7 +6733,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6768,8 +6768,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6819,12 +6819,12 @@
       <c r="K61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="8" t="inlineStr">
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6832,7 +6832,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6918,12 +6918,12 @@
       <c r="K62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L62" s="8" t="inlineStr">
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6931,7 +6931,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7022,7 +7022,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7030,7 +7030,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7051,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63" s="9" t="n">
         <v>1</v>
@@ -7121,7 +7121,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7129,7 +7129,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7215,12 +7215,12 @@
       <c r="K65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="8" t="inlineStr">
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7228,7 +7228,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7314,12 +7314,12 @@
       <c r="K66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="8" t="inlineStr">
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7327,7 +7327,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7344,8 +7344,8 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
@@ -7413,12 +7413,12 @@
       <c r="K67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7426,7 +7426,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7512,12 +7512,12 @@
       <c r="K68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="8" t="inlineStr">
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7525,7 +7525,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7616,7 +7616,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7624,7 +7624,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7710,12 +7710,12 @@
       <c r="K70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="8" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7723,7 +7723,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7809,12 +7809,12 @@
       <c r="K71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="8" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7822,7 +7822,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7908,12 +7908,12 @@
       <c r="K72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="8" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7921,7 +7921,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8007,12 +8007,12 @@
       <c r="K73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="8" t="inlineStr">
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8020,7 +8020,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8106,12 +8106,12 @@
       <c r="K74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="8" t="inlineStr">
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8119,7 +8119,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8205,12 +8205,12 @@
       <c r="K75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="8" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8218,7 +8218,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8304,12 +8304,12 @@
       <c r="K76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="8" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8317,7 +8317,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8403,12 +8403,12 @@
       <c r="K77" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L77" s="8" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8416,7 +8416,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8430,14 +8430,14 @@
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="9" t="n">
-        <v>1</v>
+      <c r="S77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T77" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U77" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V77" s="9" t="n">
         <v>1</v>
@@ -8507,7 +8507,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8515,7 +8515,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8601,12 +8601,12 @@
       <c r="K79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="8" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8614,7 +8614,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8705,7 +8705,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8713,7 +8713,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8791,52 +8791,52 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K81" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N81" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O81" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -8903,7 +8903,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -8911,7 +8911,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9003,12 +9003,12 @@
       <c r="K83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="8" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9016,7 +9016,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9051,8 +9051,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9121,7 +9121,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9213,12 +9213,12 @@
       <c r="K85" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="8" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9226,7 +9226,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9261,8 +9261,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9310,20 +9310,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9331,7 +9331,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9355,7 +9355,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9424,7 +9424,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9432,7 +9432,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9520,12 +9520,12 @@
       <c r="K88" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L88" s="8" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9533,7 +9533,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9621,12 +9621,12 @@
       <c r="K89" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L89" s="8" t="inlineStr">
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9634,7 +9634,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9726,12 +9726,12 @@
       <c r="K90" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L90" s="8" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9739,7 +9739,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9827,12 +9827,12 @@
       <c r="K91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9840,7 +9840,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9932,12 +9932,12 @@
       <c r="K92" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="8" t="inlineStr">
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9945,7 +9945,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10038,7 +10038,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10046,7 +10046,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10134,12 +10134,12 @@
       <c r="K94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L94" s="8" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10147,7 +10147,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10239,12 +10239,12 @@
       <c r="K95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L95" s="8" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10252,7 +10252,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10344,12 +10344,12 @@
       <c r="K96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="8" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10357,7 +10357,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10445,12 +10445,12 @@
       <c r="K97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L97" s="8" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10458,7 +10458,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10493,8 +10493,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10551,7 +10551,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10559,7 +10559,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10651,12 +10651,12 @@
       <c r="K99" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L99" s="8" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10755,7 +10755,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10763,7 +10763,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10841,20 +10841,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -10862,7 +10862,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10897,8 +10897,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10948,12 +10948,12 @@
       <c r="K102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L102" s="8" t="inlineStr">
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -10961,7 +10961,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10996,8 +10996,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11047,12 +11047,12 @@
       <c r="K103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="8" t="inlineStr">
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11060,7 +11060,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11095,8 +11095,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11146,12 +11146,12 @@
       <c r="K104" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L104" s="8" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11159,7 +11159,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11245,12 +11245,12 @@
       <c r="K105" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L105" s="8" t="inlineStr">
+      <c r="L105" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11258,7 +11258,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11344,12 +11344,12 @@
       <c r="K106" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="8" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -11357,7 +11357,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11448,7 +11448,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11456,7 +11456,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11465,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11542,12 +11542,12 @@
       <c r="K108" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="8" t="inlineStr">
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="M108" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11555,7 +11555,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11619,7 +11619,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11646,7 +11646,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M109" s="7" t="n">
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11654,7 +11654,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11689,8 +11689,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11745,7 +11745,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11753,7 +11753,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11839,12 +11839,12 @@
       <c r="K111" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L111" s="8" t="inlineStr">
+      <c r="L111" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -11852,7 +11852,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11938,12 +11938,12 @@
       <c r="K112" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L112" s="8" t="inlineStr">
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M112" s="7" t="n">
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -11951,7 +11951,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11986,8 +11986,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12037,12 +12037,12 @@
       <c r="K113" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L113" s="8" t="inlineStr">
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -12050,7 +12050,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12136,12 +12136,12 @@
       <c r="K114" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L114" s="8" t="inlineStr">
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -12149,7 +12149,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12184,8 +12184,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12235,12 +12235,12 @@
       <c r="K115" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L115" s="8" t="inlineStr">
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -12248,7 +12248,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12283,8 +12283,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12334,12 +12334,12 @@
       <c r="K116" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L116" s="8" t="inlineStr">
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="M116" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -12347,7 +12347,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12438,7 +12438,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12446,7 +12446,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12532,12 +12532,12 @@
       <c r="K118" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L118" s="8" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12631,12 +12631,12 @@
       <c r="K119" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="8" t="inlineStr">
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M119" s="7" t="n">
+      <c r="M119" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12644,7 +12644,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12730,12 +12730,12 @@
       <c r="K120" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L120" s="8" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12743,7 +12743,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12829,12 +12829,12 @@
       <c r="K121" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="8" t="inlineStr">
+      <c r="L121" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -12842,7 +12842,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12898,7 +12898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12962,31 +12962,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -13000,26 +13000,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -13033,29 +13033,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -13066,62 +13066,62 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -13132,26 +13132,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -13165,29 +13165,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -13198,62 +13198,62 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -13264,14 +13264,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13283,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -13297,14 +13297,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13330,14 +13330,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13349,43 +13349,43 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -13418,7 +13418,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -13429,29 +13429,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13462,14 +13462,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13481,40 +13481,40 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
@@ -13528,20 +13528,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -13550,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -13561,20 +13561,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -13594,14 +13594,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13622,25 +13622,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -13660,14 +13660,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13679,10 +13679,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -13693,29 +13693,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -13726,66 +13726,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="10" t="n">
         <v>2</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2003,11 +2003,11 @@
         </is>
       </c>
       <c r="M13" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
@@ -2048,8 +2048,8 @@
       <c r="Z13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA13" s="9" t="n">
-        <v>0</v>
+      <c r="AA13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB13" s="4" t="n">
         <v>9</v>
@@ -3205,17 +3205,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3648,8 +3648,8 @@
       <c r="V29" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>3</v>
+      <c r="W29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3837,8 +3837,8 @@
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>2</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4635,8 +4635,8 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>2</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5694,13 +5694,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5738,8 +5738,8 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>3</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6001,13 +6001,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9137,8 +9137,8 @@
       <c r="T84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>1</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9411,17 +9411,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9455,11 +9455,11 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
+      <c r="V87" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W87" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>7</v>
@@ -9613,13 +9613,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -11338,13 +11338,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11571,11 +11571,11 @@
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
@@ -11932,13 +11932,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12328,13 +12328,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12372,11 +12372,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="9" t="n">
         <v>2</v>
@@ -12625,13 +12625,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -13255,7 +13255,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -13273,13 +13273,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -13339,7 +13339,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13636,7 +13636,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13669,7 +13669,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -13801,13 +13801,13 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/77/inyear.xlsx
+++ b/docs/d/77/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1403,8 +1403,8 @@
       <c r="Q7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>1</v>
+      <c r="R7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S7" s="10" t="n">
         <v>2</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>5</v>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4224,8 +4224,8 @@
       <c r="P35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
-        <v>1</v>
+      <c r="Q35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="9" t="n">
         <v>0</v>
@@ -7110,13 +7110,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8895,10 +8895,10 @@
         <v>7</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>1</v>
       </c>
       <c r="U105" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V105" s="9" t="n">
         <v>1</v>
@@ -11338,13 +11338,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11536,17 +11536,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11635,13 +11635,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-13</v>
+        <v>1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11836,14 +11836,14 @@
         <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12075,8 +12075,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12258,8 +12258,8 @@
       <c r="P115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
+      <c r="Q115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -13108,7 +13108,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -13306,7 +13306,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
